--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260903_215901.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260903_215901.xlsx
@@ -6402,7 +6402,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260903_215901.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260903_215901.xlsx
@@ -6402,7 +6402,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
